--- a/공정모델링/2차_void정확도_DOE.xlsx
+++ b/공정모델링/2차_void정확도_DOE.xlsx
@@ -72,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -84,6 +84,15 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1704,7 +1713,6 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
           <t>→ 안전창: kV≤60(또는 정점) + R을 극단(0.35·0.65)으로 몰지 않기. 운영점 kV60·R0.5 = 완전 청정.</t>
@@ -2256,7 +2264,6 @@
       <c r="I15" t="n">
         <v>2</v>
       </c>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2292,7 +2299,6 @@
       <c r="I16" t="n">
         <v>3</v>
       </c>
-      <c r="L16" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2308,34 +2314,75 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="115" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PhaseC — False OK(진짜 void 미검출) : 보류</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>PhaseC — False OK(진짜 void 미검출): 전 데이터셋 검토 결과</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>가장 중요한 오류(진짜 불량을 OK로 놓침)는 '진짜 void가 있는 샘플'이 있어야만 검증된다. 현재 2자재·웨이퍼는 void≈0(있는 건 전부 kV62 아티팩트)이라 검증 불가. → 불량 웨이퍼 또는 인위 void 샘플 확보 시 진행. 그 전까지 'False OK 미검증'을 모델 한계로 명시.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>■ 4개 데이터셋(DOE·TB500M·TEST·43런) 전수 확인 — 모두 같은 웨이퍼(126173086.17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>void는 전량 Q_dia&lt;0.9(undersize) 조건의 아티팩트. void%가 undersize 정도에 비례(Q0.88→18.7%). Q정상(kV60·Q≈0.98)에선 void=0(예외: F32 3/2988·≤1%, 노이즈 추정). → 이 웨이퍼는 실제로 void가 없다.</t>
+        </is>
+      </c>
+    </row>
     <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>■ '0.1% threshold로 계산해 8%에 적용' 검토</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>방향은 타당: 시스템이 0.1%(≈1.6px)를 (아티팩트로라도) 잡으면 8% void(≈14.7px)는 훨씬 쉽게 잡음 → 감도부족으로 8% 놓칠(False OK) 가능성 낮음. 한계 3: ①진짜 void가 0.1%조차 없어 시험 대상 없음 ②그 감도는 나쁜조건(kV62)에서 본 것, 운영조건(kV60) 감도는 미실측 ③오차는 2/N이라 0.1%(오차125%)와 8%(오차13.6%)는 규모가 달라 수치 대입 불가(검출 여부에만 방향 적용).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>■ 결론</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>False OK 위험 = 감도상 낮음, 그러나 미검증(진짜 void 부재). 확정엔 '소형이라도 진짜 void 있는 샘플' 1개면 충분(kV60에서 잡는지 확인). 그 전까지 운영조건 kV60·R적정에서 거짓void=0(전 데이터 확인)이라 실무상 안전, False OK는 '미검증 한계'로 명시.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:H6"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/공정모델링/2차_void정확도_DOE.xlsx
+++ b/공정모델링/2차_void정확도_DOE.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설계_설명" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기존데이터_활용_PhaseA" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PhaseB_경계정밀화_신규" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PhaseC_FalseOK_보류" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="교호작용_현황" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PhaseC_FalseOK_보류" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +60,11 @@
         <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6E0B4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -72,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -92,6 +98,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -510,12 +528,12 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>② 경계 정밀화 = 소수 신규</t>
+          <t>② 경계 정밀화 + R×F 해소 = 소수 신규(통합)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>거짓void가 시작되는 kV·R 경계(안전창)만 촘촘히 — 기존 2자재로 가능(void 샘플 불필요). 'PhaseB' ~12런.</t>
+          <t>거짓void가 시작되는 kV·R 경계(안전창) + 기존 데이터의 R×F 교락(R=0.35/0.65가 F 한 값에만 존재)을 같은 실험으로 동시 해소 — 기존 2자재로 가능(void 샘플 불필요). 'PhaseB' 16런(경계9+반복3+R×F4). 직경 쪽 Phase B1과 통합돼 별도 실험 불필요. 교호작용 전체 판정은 '교호작용_현황' 시트 참조.</t>
         </is>
       </c>
     </row>
@@ -1733,148 +1751,137 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PhaseB — 거짓void 안전창 정밀화 (기존 2자재로 가능, void 샘플 불필요)</t>
+          <t>PhaseB — 거짓void 경계정밀화 + R×F 교호작용 해소 (직경 Phase B1과 통합, 기존 2자재로 가능)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>목적: kV60↔62, R0.4↔0.65 사이 어디서 거짓void가 시작되나(안전 마진). 운영점은 반복으로 σ.</t>
-        </is>
-      </c>
-    </row>
+          <t>목적1(경계매핑): kV60↔62 · R0.4↔0.6 사이 어디서 거짓void가 시작되나(안전 마진 확인). 목적2(R×F 해소): 기존 데이터는 R=0.35가 F=128, R=0.65가 F=32(또는 F=64)로만 테스트돼 R의 효과와 F의 효과가 교락(confound)돼 있음 — 이 4셀은 그 짝을 채워 직경 Phase B1과 거짓NG 확인을 동시에 해결.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Run</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Phase</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>자재</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>PD</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>kV</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>반복#</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>목적</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>거짓NG율%(측정)</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Q_dia(측정)</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>void%σ(자동)</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>PhaseB</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>26µm</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>26</v>
-      </c>
-      <c r="E5" t="n">
-        <v>60</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>64</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>kV60×R0.4 거짓void 경계</t>
-        </is>
-      </c>
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PhaseB</t>
+          <t>B-Grid</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1889,7 +1896,7 @@
         <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G6" t="n">
         <v>64</v>
@@ -1900,21 +1907,26 @@
       <c r="I6" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>kV60×R0.5 거짓void 경계</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>경계매핑</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>kV60×R0.4 거짓void 경계</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PhaseB</t>
+          <t>B-Grid</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1929,7 +1941,7 @@
         <v>60</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G7" t="n">
         <v>64</v>
@@ -1940,21 +1952,26 @@
       <c r="I7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>kV60×R0.6 거짓void 경계</t>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>경계매핑</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>kV60×R0.5 거짓void 경계(운영점 근접)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PhaseB</t>
+          <t>B-Grid</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1966,10 +1983,10 @@
         <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G8" t="n">
         <v>64</v>
@@ -1980,21 +1997,26 @@
       <c r="I8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>kV61×R0.4 거짓void 경계</t>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>경계매핑</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>kV60×R0.6 거짓void 경계</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PhaseB</t>
+          <t>B-Grid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2009,7 +2031,7 @@
         <v>61</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G9" t="n">
         <v>64</v>
@@ -2020,21 +2042,26 @@
       <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>kV61×R0.5 거짓void 경계</t>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>경계매핑</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>kV61×R0.4 거짓void 경계</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PhaseB</t>
+          <t>B-Grid</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2049,7 +2076,7 @@
         <v>61</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
         <v>64</v>
@@ -2060,21 +2087,26 @@
       <c r="I10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>kV61×R0.6 거짓void 경계</t>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>경계매핑</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>kV61×R0.5 거짓void 경계</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>G6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PhaseB</t>
+          <t>B-Grid</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2086,10 +2118,10 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G11" t="n">
         <v>64</v>
@@ -2100,21 +2132,26 @@
       <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>kV62×R0.4 거짓void 경계</t>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>경계매핑</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>kV61×R0.6 거짓void 경계</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>G7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PhaseB</t>
+          <t>B-Grid</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2129,7 +2166,7 @@
         <v>62</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G12" t="n">
         <v>64</v>
@@ -2140,21 +2177,26 @@
       <c r="I12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>kV62×R0.5 거짓void 경계</t>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>경계매핑</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>kV62×R0.4 거짓void 경계</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>G8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PhaseB</t>
+          <t>B-Grid</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2169,7 +2211,7 @@
         <v>62</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G13" t="n">
         <v>64</v>
@@ -2180,21 +2222,26 @@
       <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>kV62×R0.6 거짓void 경계</t>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>경계매핑</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>kV62×R0.5 거짓void 경계(기존 D26-05=0% 재확인)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rep</t>
+          <t>G9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PhaseB</t>
+          <t>B-Grid</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2206,10 +2253,10 @@
         <v>26</v>
       </c>
       <c r="E14" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G14" t="n">
         <v>64</v>
@@ -2220,25 +2267,26 @@
       <c r="I14" t="n">
         <v>1</v>
       </c>
-      <c r="K14">
-        <f>IFERROR(STDEV(J14:J16),"")</f>
-        <v/>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>운영점 반복 — void%σ(≈0 확인)</t>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>경계매핑</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>kV62×R0.6 거짓void 경계</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rep</t>
+          <t>Rep1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PhaseB</t>
+          <t>B-Rep</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2262,18 +2310,28 @@
         <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>운영점σ</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>운영점 반복1</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rep</t>
+          <t>Rep2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PhaseB</t>
+          <t>B-Rep</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2297,12 +2355,265 @@
         <v>4</v>
       </c>
       <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>운영점σ</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>운영점 반복2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Rep3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>B-Rep</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>26µm</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>26</v>
+      </c>
+      <c r="E17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>64</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
         <v>3</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>운영점σ</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>운영점 반복3(σ 계산용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="M18">
+        <f>IFERROR(STDEV(K15:K17),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>RF1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>B-RF</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>26µm</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>26</v>
+      </c>
+      <c r="E19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G19" t="n">
+        <v>32</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>R×F(직경)</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>기존 kV60·R0.35·F128(D26-06, Q=0.996)과 짝 — F32에서도 Q_dia 유지되나(직경 Phase B1 겸용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>RF2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>B-RF</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>26µm</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>26</v>
+      </c>
+      <c r="E20" t="n">
+        <v>62</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G20" t="n">
+        <v>32</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>R×F(거짓NG)</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>기존 kV62·R0.35·F128(D26-15, 거짓NG 9.89%)과 짝 — F32에서 거짓NG 악화/개선되나</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>RF3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>B-RF</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>26µm</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>26</v>
+      </c>
+      <c r="E21" t="n">
+        <v>60</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>32</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>R×F(직경)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>기존 kV60·R0.65·F64(D26-07, Q=0.978)와 짝 — F32에서도 유지되나</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>RF4</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>B-RF</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>26µm</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>26</v>
+      </c>
+      <c r="E22" t="n">
+        <v>62</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G22" t="n">
+        <v>64</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>R×F(거짓NG)</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>기존 kV62·R0.65·F32(D26-17, 거짓NG 8.43%)와 짝 — F64로 올리면 거짓NG 개선되나</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>요약</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>총 신규 16런 = 경계매핑 9 + 운영점반복 3 + R×F 교락해소 4. R×F 4런은 직경(Phase B1)과 거짓NG(PhaseA 교락 해소)를 동시에 답함 — 별도 실험 불필요.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A2:L3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2314,7 +2625,328 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>파라미터 교호작용 현황 — kV·R·F·W 6개 쌍 전수 판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>대상 응답변수 2개: 직경정확도(Q_dia) / 거짓void율(False NG%). 상태는 기존 38런 실측 + 신규 PhaseB-RF(예정) 기준.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>교호작용</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>대상</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>우선순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>kV×R</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>거짓void</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>검증됨(있음)</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>kV62+R극단(0.35·0.65)만 거짓NG 8~10%, 같은 kV62라도 R0.5는 0%(D26-05/13/19) → 실제 상호작용</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>kV×R</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>직경</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>검증됨(불필요)</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>R의 직경 주효과 자체가 Δ≤2.1%p로 미미(4번그래프) → 교호작용을 논할 실익 적음</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>kV×F</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>거짓void</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>검증됨(없음)</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>kV62·R0.5에서 F32/64/128 전부 거짓NG 0%(D26-05/13/19) → 상호작용 없음 확인</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>kV×W</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>거짓void</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>검증됨(없음)</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>kV62·R0.5에서 W4/6 전부 거짓NG 0%(D26-05/10 계열) → 상호작용 없음 확인</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>R×F</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>직경+거짓void</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>미검증→해소 예정</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>R0.35=F128뿐, R0.65=F32/64뿐(교락) → 어느 쪽 효과인지 분리 불가. PhaseB-RF 4런(RF1~4)으로 직경·거짓NG 동시 해소</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>최우선(예정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>R×W</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>직경+거짓void</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>미검증(보류)</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>R극단에서 W도 한 값만 테스트(교락). W 주효과가 F보다도 작아(편차 F0.28%p&gt;W0.03%p) 물리적 우선순위 낮음 → 보류</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>F×W</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>직경+거짓void</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>확인불가(무의미)</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>안전구간(kV60·R0.5)에서만 F/W 다양하게 조합됨 — 반응이 전부 0/무변화라 상호작용 자체를 정의할 변동이 없음</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>kV×자재(D)</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>직경</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>검증됨</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>2anchor(26·86µm) 각각 kV*≈60 — kV*(D) 직선의 기울기 -0.00117로 사실상 자재 무관</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>R×자재(D)</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>직경+거짓void</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>검증됨(정의 관계)</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>R=D·√0.08/N8_MIN 자체가 D 의존 공식 — 별도로 검증할 상호작용이 아니라 설계에 내재된 관계</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>결론</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>kV×R(거짓void)만 실제 신호가 있었고, kV×F/kV×W는 이미 반증됨(효과없음 확인). R×F는 원본 DOE의 설계 교락 때문에 미검증 상태였는데, 이번에 PhaseB-RF로 해소 예정. R×W는 물리적 우선순위가 낮아 보류, F×W는 응답 자체가 무변화라 검증 불가능(무의미).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B15:E15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="115" customWidth="1" min="1" max="1"/>
@@ -2341,7 +2973,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -2356,8 +2987,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
@@ -2372,16 +3001,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/공정모델링/2차_void정확도_DOE.xlsx
+++ b/공정모델링/2차_void정확도_DOE.xlsx
@@ -1751,7 +1751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1912,6 +1912,12 @@
           <t>경계매핑</t>
         </is>
       </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.9932</v>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>kV60×R0.4 거짓void 경계</t>
@@ -1957,6 +1963,12 @@
           <t>경계매핑</t>
         </is>
       </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.9879</v>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>kV60×R0.5 거짓void 경계(운영점 근접)</t>
@@ -2002,6 +2014,12 @@
           <t>경계매핑</t>
         </is>
       </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.9737</v>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>kV60×R0.6 거짓void 경계</t>
@@ -2047,6 +2065,12 @@
           <t>경계매핑</t>
         </is>
       </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.8293</v>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>kV61×R0.4 거짓void 경계</t>
@@ -2092,6 +2116,12 @@
           <t>경계매핑</t>
         </is>
       </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.7517</v>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>kV61×R0.5 거짓void 경계</t>
@@ -2137,6 +2167,12 @@
           <t>경계매핑</t>
         </is>
       </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.8073</v>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>kV61×R0.6 거짓void 경계</t>
@@ -2182,6 +2218,12 @@
           <t>경계매핑</t>
         </is>
       </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.7895</v>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>kV62×R0.4 거짓void 경계</t>
@@ -2227,6 +2269,12 @@
           <t>경계매핑</t>
         </is>
       </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.785</v>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>kV62×R0.5 거짓void 경계(기존 D26-05=0% 재확인)</t>
@@ -2272,6 +2320,12 @@
           <t>경계매핑</t>
         </is>
       </c>
+      <c r="K14" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.8716</v>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>kV62×R0.6 거짓void 경계</t>
@@ -2317,6 +2371,12 @@
           <t>운영점σ</t>
         </is>
       </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.9841</v>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>운영점 반복1</t>
@@ -2362,6 +2422,12 @@
           <t>운영점σ</t>
         </is>
       </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.9862</v>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>운영점 반복2</t>
@@ -2406,6 +2472,12 @@
         <is>
           <t>운영점σ</t>
         </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.9867</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -2458,6 +2530,12 @@
           <t>R×F(직경)</t>
         </is>
       </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.9945000000000001</v>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>기존 kV60·R0.35·F128(D26-06, Q=0.996)과 짝 — F32에서도 Q_dia 유지되나(직경 Phase B1 겸용)</t>
@@ -2503,6 +2581,12 @@
           <t>R×F(거짓NG)</t>
         </is>
       </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.7897</v>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>기존 kV62·R0.35·F128(D26-15, 거짓NG 9.89%)과 짝 — F32에서 거짓NG 악화/개선되나</t>
@@ -2548,6 +2632,12 @@
           <t>R×F(직경)</t>
         </is>
       </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.9668</v>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>기존 kV60·R0.65·F64(D26-07, Q=0.978)와 짝 — F32에서도 유지되나</t>
@@ -2593,6 +2683,12 @@
           <t>R×F(거짓NG)</t>
         </is>
       </c>
+      <c r="K22" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.8241000000000001</v>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>기존 kV62·R0.65·F32(D26-17, 거짓NG 8.43%)와 짝 — F64로 올리면 거짓NG 개선되나</t>
@@ -2611,9 +2707,22 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>⚠ 이상신호</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>kV61(G4~6) 실측 Q_dia=0.75~0.83이 회귀모델 예측(≈0.93, kV60·62 사이 보간)보다 뚜렷이 낮고 kV62(G7~9, Q=0.79~0.87)와 겹침 — 포물선상 기대와 어긋남. 원인 미확인(계산기 오류/실제 kV 드리프트/자재 편차 등 후속 확인 필요). 자세한 내용은 대화 기록 참조.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:L3"/>
+    <mergeCell ref="B26:N26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/공정모델링/2차_void정확도_DOE.xlsx
+++ b/공정모델링/2차_void정확도_DOE.xlsx
@@ -2707,15 +2707,15 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="90" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>⚠ 이상신호</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>kV61(G4~6) 실측 Q_dia=0.75~0.83이 회귀모델 예측(≈0.93, kV60·62 사이 보간)보다 뚜렷이 낮고 kV62(G7~9, Q=0.79~0.87)와 겹침 — 포물선상 기대와 어긋남. 원인 미확인(계산기 오류/실제 kV 드리프트/자재 편차 등 후속 확인 필요). 자세한 내용은 대화 기록 참조.</t>
+          <t>■ kV 창(window) 발견</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>PhaseB로 kV60/61/62 실측 → 파라미터 이상 아님(장비 die-level 평균과 일치). 핵심 발견: kV60 정점이 1차 3점(58/60/62) 포물선이 그린 것보다 훨씬 날카롭다. kV60=Q0.97~0.99인데 kV61에서 이미 Q0.75~0.83(≈20µm, 언더사이즈)로 급락 — 포물선 보간(kV61≈0.93)과 크게 다름. kV61·kV62가 거의 같은 언더사이즈 대역이고 61&lt;62인 R도 있음(정점 이탈 시 응답 불안정). → 결론: 양호 kV창은 좁다(사실상 kV60 ±0.5). 레시피의 ±1kV 트림 안내는 과대 — kV61이면 이미 ~20% 언더. kV 캘리브레이션/드리프트 관리가 직경 정확도의 최대 리스크.</t>
         </is>
       </c>
     </row>

--- a/공정모델링/2차_void정확도_DOE.xlsx
+++ b/공정모델링/2차_void정확도_DOE.xlsx
@@ -2758,6 +2758,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -2894,29 +2895,29 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>R×F</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>직경+거짓void</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>미검증→해소 예정</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>R0.35=F128뿐, R0.65=F32/64뿐(교락) → 어느 쪽 효과인지 분리 불가. PhaseB-RF 4런(RF1~4)으로 직경·거짓NG 동시 해소</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>최우선(예정)</t>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>✅ 해소완료(PhaseB)</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>직경: R0.35·F32(RF1)=Q0.9945 ≈ R0.35·F128(D26-06)=Q0.9961 → 극단R에서도 F는 직경 무영향(가법모델 유지). 보너스: RF1(kV60·R0.35·F32)=Q0.9945·N8 20.9·거짓NG0% → R0.35이 F32에서 완벽 작동(기존 F128 필요없음). 거짓NG: kV62·R0.65에서 F32(D26-17)8.43%→F64(RF4)2.64%로 고F가 거짓NG 저감 — 단 이는 회피대역(kV62) 얘기.</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -3028,6 +3029,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
@@ -3036,7 +3038,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>kV×R(거짓void)만 실제 신호가 있었고, kV×F/kV×W는 이미 반증됨(효과없음 확인). R×F는 원본 DOE의 설계 교락 때문에 미검증 상태였는데, 이번에 PhaseB-RF로 해소 예정. R×W는 물리적 우선순위가 낮아 보류, F×W는 응답 자체가 무변화라 검증 불가능(무의미).</t>
+          <t>kV×R(거짓void 있음)·kV×F/kV×W(없음)은 기존 데이터로 확정. R×F는 PhaseB로 해소완료 — 직경엔 F 무영향(극단R 포함), 거짓NG는 회피대역에서만 고F가 완화. R0.35은 F32에서 작동 확인(N8 20.9 여유). 남은 미검증은 R×W(우선순위 낮음)뿐. F×W는 응답 무변화로 정의 불가.</t>
         </is>
       </c>
     </row>

--- a/공정모델링/2차_void정확도_DOE.xlsx
+++ b/공정모델링/2차_void정확도_DOE.xlsx
@@ -2922,29 +2922,29 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>R×W</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>직경+거짓void</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>미검증(보류)</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>R극단에서 W도 한 값만 테스트(교락). W 주효과가 F보다도 작아(편차 F0.28%p&gt;W0.03%p) 물리적 우선순위 낮음 → 보류</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>낮음</t>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>직경</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>✅ 해소완료(기존데이터)</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>86µm kV60.5·F64에 R{0.8,1.5}×W{4,6} 2×2 코너가 이미 존재(D86-01/02/03·10·07·11). 교호작용=0.14%p(노이즈 수준). W효과 R0.8=-0.45%p, R1.5=-0.59%p로 거의 동일 → R×W 없음. 신규런 0.</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>kV×R(거짓void 있음)·kV×F/kV×W(없음)은 기존 데이터로 확정. R×F는 PhaseB로 해소완료 — 직경엔 F 무영향(극단R 포함), 거짓NG는 회피대역에서만 고F가 완화. R0.35은 F32에서 작동 확인(N8 20.9 여유). 남은 미검증은 R×W(우선순위 낮음)뿐. F×W는 응답 무변화로 정의 불가.</t>
+          <t>직경·거짓NG 관점 교호작용은 전부 확정: kV×R(있음)·kV×F/kV×W(없음)·R×F(해소)·R×W(해소,0.14%p)·F×W(정의불가). 남은 미지수는 교호작용이 아니라 응답변수 하나 — 진짜 void 검출(False OK). 이건 어떤 교호작용을 더 봐도 안 풀리고 void 샘플이 있어야만 함.</t>
         </is>
       </c>
     </row>
